--- a/branches/dev/StructureDefinition-mii-pr-pro-observation-bdi-ii.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-pro-observation-bdi-ii.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T15:01:16+00:00</t>
+    <t>2026-10-14T08:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-pro-observation-bdi-ii.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-pro-observation-bdi-ii.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T08:51:14+00:00</t>
+    <t>2026-10-19T03:43:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-pro-observation-bdi-ii.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-pro-observation-bdi-ii.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T03:43:18+00:00</t>
+    <t>2026-10-19T04:09:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-pro-observation-bdi-ii.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-pro-observation-bdi-ii.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T04:09:45+00:00</t>
+    <t>2026-10-19T22:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-pro-observation-bdi-ii.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-pro-observation-bdi-ii.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:04:08+00:00</t>
+    <t>2026-10-19T22:28:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
